--- a/extenbooks/XS002_extenbook.xlsx
+++ b/extenbooks/XS002_extenbook.xlsx
@@ -903,7 +903,7 @@
         <v>24.26700000000002</v>
       </c>
       <c r="D6" t="n">
-        <v>20.64184536082473</v>
+        <v>20.64184536082474</v>
       </c>
       <c r="E6" t="n">
         <v>30.30337862900169</v>
@@ -981,7 +981,7 @@
         <v>30.941</v>
       </c>
       <c r="D9" t="n">
-        <v>25.97801875</v>
+        <v>25.97801874999999</v>
       </c>
       <c r="E9" t="n">
         <v>35.55068966543091</v>
@@ -1134,7 +1134,7 @@
         <v>50.2</v>
       </c>
       <c r="C15" t="n">
-        <v>36.46800000000008</v>
+        <v>36.46800000000007</v>
       </c>
       <c r="D15" t="n">
         <v>33.24044531633152</v>
@@ -1169,7 +1169,7 @@
         <v>42.95298199052133</v>
       </c>
       <c r="F16" t="n">
-        <v>19.57235998271392</v>
+        <v>19.57235998271391</v>
       </c>
       <c r="G16" t="n">
         <v>51.1</v>
@@ -1192,7 +1192,7 @@
         <v>32.21911092646448</v>
       </c>
       <c r="E17" t="n">
-        <v>43.77963375485327</v>
+        <v>43.77963375485326</v>
       </c>
       <c r="F17" t="n">
         <v>18.48088907353552</v>
@@ -1221,7 +1221,7 @@
         <v>44.47656366585564</v>
       </c>
       <c r="F18" t="n">
-        <v>18.78984340770792</v>
+        <v>18.78984340770791</v>
       </c>
       <c r="G18" t="n">
         <v>50.9</v>
@@ -1253,7 +1253,7 @@
         <v>58.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3.600682593856656</v>
+        <v>3.600682593856655</v>
       </c>
     </row>
     <row r="20">
@@ -1429,7 +1429,7 @@
         <v>57.96568546576879</v>
       </c>
       <c r="F26" t="n">
-        <v>24.16788360128617</v>
+        <v>24.16788360128618</v>
       </c>
       <c r="G26" t="n">
         <v>87.90000000000001</v>
@@ -1461,7 +1461,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>5.307692307692308</v>
+        <v>5.307692307692307</v>
       </c>
     </row>
     <row r="28">
@@ -1539,7 +1539,7 @@
         <v>109.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.871350364963504</v>
+        <v>4.871350364963503</v>
       </c>
     </row>
     <row r="31">
@@ -1680,7 +1680,7 @@
         <v>181.1</v>
       </c>
       <c r="C36" t="n">
-        <v>100.8139999999998</v>
+        <v>100.8139999999999</v>
       </c>
       <c r="D36" t="n">
         <v>136.768343530964</v>
@@ -1764,7 +1764,7 @@
         <v>139.8255161224351</v>
       </c>
       <c r="E39" t="n">
-        <v>195.1049007659868</v>
+        <v>195.1049007659867</v>
       </c>
       <c r="F39" t="n">
         <v>34.97448387756495</v>
@@ -1839,7 +1839,7 @@
         <v>151.1699999999996</v>
       </c>
       <c r="D42" t="n">
-        <v>185.0835726210352</v>
+        <v>185.0835726210351</v>
       </c>
       <c r="E42" t="n">
         <v>233.6549190302999</v>
@@ -1862,13 +1862,13 @@
         <v>262.6</v>
       </c>
       <c r="C43" t="n">
-        <v>158.7970000000001</v>
+        <v>158.797</v>
       </c>
       <c r="D43" t="n">
         <v>204.5789705277931</v>
       </c>
       <c r="E43" t="n">
-        <v>244.9544067020716</v>
+        <v>244.9544067020715</v>
       </c>
       <c r="F43" t="n">
         <v>58.02102947220692</v>
@@ -1955,7 +1955,7 @@
         <v>358.4</v>
       </c>
       <c r="H46" t="n">
-        <v>5.826729910714287</v>
+        <v>5.826729910714286</v>
       </c>
     </row>
     <row r="47">
@@ -2018,7 +2018,7 @@
         <v>414.9</v>
       </c>
       <c r="C49" t="n">
-        <v>226.3560000000003</v>
+        <v>226.3560000000002</v>
       </c>
       <c r="D49" t="n">
         <v>317.9531645822911</v>
@@ -2070,7 +2070,7 @@
         <v>485.1</v>
       </c>
       <c r="C51" t="n">
-        <v>253.94</v>
+        <v>253.9400000000001</v>
       </c>
       <c r="D51" t="n">
         <v>357.413675551788</v>
@@ -2209,7 +2209,7 @@
         <v>436.3638988079471</v>
       </c>
       <c r="F56" t="n">
-        <v>186.4730557821883</v>
+        <v>186.4730557821882</v>
       </c>
       <c r="G56" t="n">
         <v>734.8</v>
@@ -2592,14 +2592,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B75" t="n">
-        <v>22.99199999999999</v>
+        <v>39.2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2615,14 +2615,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="B76" t="n">
-        <v>22.13317399617591</v>
+        <v>34.6</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2638,14 +2638,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B77" t="n">
-        <v>27.89235982558716</v>
+        <v>37.5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2661,14 +2661,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="B78" t="n">
-        <v>12.36682600382409</v>
+        <v>42.7</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2684,14 +2684,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="B79" t="n">
-        <v>22.5</v>
+        <v>43.1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2707,14 +2707,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1947</v>
+        <v>1953</v>
       </c>
       <c r="B80" t="n">
-        <v>3.648888888888889</v>
+        <v>42</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1948</v>
+        <v>1954</v>
       </c>
       <c r="B81" t="n">
-        <v>39.2</v>
+        <v>42.3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2753,14 +2753,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1948</v>
+        <v>1955</v>
       </c>
       <c r="B82" t="n">
-        <v>24.85599999999999</v>
+        <v>44.3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2776,14 +2776,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1948</v>
+        <v>1956</v>
       </c>
       <c r="B83" t="n">
-        <v>23.49115492957747</v>
+        <v>45.9</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2799,14 +2799,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1948</v>
+        <v>1957</v>
       </c>
       <c r="B84" t="n">
-        <v>30.06280873588836</v>
+        <v>47.8</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2822,14 +2822,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="B85" t="n">
-        <v>15.70884507042253</v>
+        <v>50.2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2845,14 +2845,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1948</v>
+        <v>1959</v>
       </c>
       <c r="B86" t="n">
-        <v>29.6</v>
+        <v>50.3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2868,14 +2868,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1948</v>
+        <v>1960</v>
       </c>
       <c r="B87" t="n">
-        <v>3.077702702702702</v>
+        <v>50.7</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1949</v>
+        <v>1961</v>
       </c>
       <c r="B88" t="n">
-        <v>34.6</v>
+        <v>53.2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2914,14 +2914,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1949</v>
+        <v>1962</v>
       </c>
       <c r="B89" t="n">
-        <v>24.26700000000002</v>
+        <v>55.3</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2937,14 +2937,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1949</v>
+        <v>1963</v>
       </c>
       <c r="B90" t="n">
-        <v>20.64184536082473</v>
+        <v>56.5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2960,14 +2960,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1949</v>
+        <v>1964</v>
       </c>
       <c r="B91" t="n">
-        <v>30.30337862900169</v>
+        <v>59.4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2983,14 +2983,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1949</v>
+        <v>1965</v>
       </c>
       <c r="B92" t="n">
-        <v>13.95815463917527</v>
+        <v>63.9</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3006,14 +3006,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1949</v>
+        <v>1966</v>
       </c>
       <c r="B93" t="n">
-        <v>27.6</v>
+        <v>68.2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3029,14 +3029,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1949</v>
+        <v>1967</v>
       </c>
       <c r="B94" t="n">
-        <v>3.217391304347826</v>
+        <v>69.8</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1950</v>
+        <v>1968</v>
       </c>
       <c r="B95" t="n">
-        <v>37.5</v>
+        <v>74.2</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -3075,14 +3075,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1950</v>
+        <v>1969</v>
       </c>
       <c r="B96" t="n">
-        <v>26.02</v>
+        <v>77.5</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3098,14 +3098,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1950</v>
+        <v>1970</v>
       </c>
       <c r="B97" t="n">
-        <v>21.08311044327573</v>
+        <v>78.5</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3121,14 +3121,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1950</v>
+        <v>1971</v>
       </c>
       <c r="B98" t="n">
-        <v>31.9388483418088</v>
+        <v>84.7</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3144,14 +3144,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1950</v>
+        <v>1972</v>
       </c>
       <c r="B99" t="n">
-        <v>16.41688955672427</v>
+        <v>96</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3167,14 +3167,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1950</v>
+        <v>1973</v>
       </c>
       <c r="B100" t="n">
-        <v>34.4</v>
+        <v>113.6</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3190,14 +3190,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1950</v>
+        <v>1974</v>
       </c>
       <c r="B101" t="n">
-        <v>2.869186046511628</v>
+        <v>113.5</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3213,10 +3213,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1951</v>
+        <v>1975</v>
       </c>
       <c r="B102" t="n">
-        <v>42.7</v>
+        <v>119.6</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3236,14 +3236,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1951</v>
+        <v>1976</v>
       </c>
       <c r="B103" t="n">
-        <v>29.114</v>
+        <v>132.2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3259,14 +3259,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1951</v>
+        <v>1977</v>
       </c>
       <c r="B104" t="n">
-        <v>24.4311164606376</v>
+        <v>146</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3282,14 +3282,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1951</v>
+        <v>1978</v>
       </c>
       <c r="B105" t="n">
-        <v>33.74244602423543</v>
+        <v>167.5</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3305,14 +3305,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1951</v>
+        <v>1979</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2688835393624</v>
+        <v>181.1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3328,14 +3328,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1951</v>
+        <v>1980</v>
       </c>
       <c r="B107" t="n">
-        <v>39.1</v>
+        <v>173.5</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3351,14 +3351,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1951</v>
+        <v>1981</v>
       </c>
       <c r="B108" t="n">
-        <v>2.930946291560102</v>
+        <v>181.6</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3374,10 +3374,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1952</v>
+        <v>1982</v>
       </c>
       <c r="B109" t="n">
-        <v>43.1</v>
+        <v>174.8</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -3397,14 +3397,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1952</v>
+        <v>1983</v>
       </c>
       <c r="B110" t="n">
-        <v>30.941</v>
+        <v>190.7</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3420,14 +3420,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1952</v>
+        <v>1984</v>
       </c>
       <c r="B111" t="n">
-        <v>25.97801875</v>
+        <v>233.1</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3443,14 +3443,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1952</v>
+        <v>1985</v>
       </c>
       <c r="B112" t="n">
-        <v>35.55068966543091</v>
+        <v>246.1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3466,14 +3466,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1952</v>
+        <v>1986</v>
       </c>
       <c r="B113" t="n">
-        <v>17.12198125000001</v>
+        <v>262.6</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3489,14 +3489,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1952</v>
+        <v>1987</v>
       </c>
       <c r="B114" t="n">
-        <v>37</v>
+        <v>294.2</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3512,14 +3512,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1952</v>
+        <v>1988</v>
       </c>
       <c r="B115" t="n">
-        <v>3.324324324324324</v>
+        <v>334.8</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1953</v>
+        <v>1989</v>
       </c>
       <c r="B116" t="n">
-        <v>42</v>
+        <v>351.6</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3558,14 +3558,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1953</v>
+        <v>1990</v>
       </c>
       <c r="B117" t="n">
-        <v>32.34</v>
+        <v>365.1</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3581,14 +3581,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1953</v>
+        <v>1991</v>
       </c>
       <c r="B118" t="n">
-        <v>25.81271453590193</v>
+        <v>367.3</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3604,14 +3604,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1953</v>
+        <v>1992</v>
       </c>
       <c r="B119" t="n">
-        <v>36.97894610202118</v>
+        <v>414.9</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3627,14 +3627,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1953</v>
+        <v>1993</v>
       </c>
       <c r="B120" t="n">
-        <v>16.18728546409807</v>
+        <v>449.6</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3650,14 +3650,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1953</v>
+        <v>1994</v>
       </c>
       <c r="B121" t="n">
-        <v>37.3</v>
+        <v>485.1</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3673,14 +3673,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1953</v>
+        <v>1995</v>
       </c>
       <c r="B122" t="n">
-        <v>3.592493297587132</v>
+        <v>516</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1954</v>
+        <v>1996</v>
       </c>
       <c r="B123" t="n">
-        <v>42.3</v>
+        <v>583.7</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3719,14 +3719,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1954</v>
+        <v>1997</v>
       </c>
       <c r="B124" t="n">
-        <v>32.15800000000002</v>
+        <v>628.2</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3742,14 +3742,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1954</v>
+        <v>1998</v>
       </c>
       <c r="B125" t="n">
-        <v>26.22484460260972</v>
+        <v>687.5</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3765,14 +3765,14 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1954</v>
+        <v>1999</v>
       </c>
       <c r="B126" t="n">
-        <v>37.41459002647837</v>
+        <v>746.8</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3788,14 +3788,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1954</v>
+        <v>2000</v>
       </c>
       <c r="B127" t="n">
-        <v>16.07515539739027</v>
+        <v>817.5</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3811,14 +3811,14 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1954</v>
+        <v>2001</v>
       </c>
       <c r="B128" t="n">
-        <v>36.4</v>
+        <v>870.7</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3834,14 +3834,14 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1954</v>
+        <v>2002</v>
       </c>
       <c r="B129" t="n">
-        <v>3.631868131868132</v>
+        <v>890.3</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1955</v>
+        <v>2003</v>
       </c>
       <c r="B130" t="n">
-        <v>44.3</v>
+        <v>930.6</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3880,14 +3880,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1955</v>
+        <v>2004</v>
       </c>
       <c r="B131" t="n">
-        <v>33.45200000000003</v>
+        <v>1033.8</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3903,14 +3903,14 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1955</v>
+        <v>2005</v>
       </c>
       <c r="B132" t="n">
-        <v>25.34998326359831</v>
+        <v>1069.8</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3926,14 +3926,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1955</v>
+        <v>2006</v>
       </c>
       <c r="B133" t="n">
-        <v>38.59418068542845</v>
+        <v>1133</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3949,14 +3949,14 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1955</v>
+        <v>2007</v>
       </c>
       <c r="B134" t="n">
-        <v>18.95001673640169</v>
+        <v>1090.4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3972,14 +3972,14 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1955</v>
+        <v>2008</v>
       </c>
       <c r="B135" t="n">
-        <v>46.6</v>
+        <v>1097.9</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3995,14 +3995,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1955</v>
+        <v>2009</v>
       </c>
       <c r="B136" t="n">
-        <v>3.103004291845493</v>
+        <v>979.4</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4018,10 +4018,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1956</v>
+        <v>2010</v>
       </c>
       <c r="B137" t="n">
-        <v>45.9</v>
+        <v>1103.4</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -4041,14 +4041,14 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1956</v>
+        <v>2011</v>
       </c>
       <c r="B138" t="n">
-        <v>35.14200000000002</v>
+        <v>1157.3</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4064,14 +4064,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1956</v>
+        <v>1947</v>
       </c>
       <c r="B139" t="n">
-        <v>27.89066666666666</v>
+        <v>22.99199999999999</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4087,14 +4087,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1956</v>
+        <v>1948</v>
       </c>
       <c r="B140" t="n">
-        <v>40.05854873369148</v>
+        <v>24.85599999999999</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4110,14 +4110,14 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1956</v>
+        <v>1949</v>
       </c>
       <c r="B141" t="n">
-        <v>18.00933333333334</v>
+        <v>24.26700000000002</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4133,14 +4133,14 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="B142" t="n">
-        <v>45.2</v>
+        <v>26.02</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4156,14 +4156,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="B143" t="n">
-        <v>3.5</v>
+        <v>29.114</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4179,14 +4179,14 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="B144" t="n">
-        <v>47.8</v>
+        <v>30.941</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4202,10 +4202,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="B145" t="n">
-        <v>36.24700000000004</v>
+        <v>32.34</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -4225,14 +4225,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="B146" t="n">
-        <v>30.07444786729856</v>
+        <v>32.15800000000002</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4248,14 +4248,14 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B147" t="n">
-        <v>41.13117066038148</v>
+        <v>33.45200000000003</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4271,14 +4271,14 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B148" t="n">
-        <v>17.72555213270143</v>
+        <v>35.14200000000002</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4297,11 +4297,11 @@
         <v>1957</v>
       </c>
       <c r="B149" t="n">
-        <v>44.5</v>
+        <v>36.24700000000004</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4317,14 +4317,14 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B150" t="n">
-        <v>3.741573033707865</v>
+        <v>36.46800000000007</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4340,14 +4340,14 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B151" t="n">
-        <v>50.2</v>
+        <v>38.33099999999999</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4363,10 +4363,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="B152" t="n">
-        <v>36.46800000000008</v>
+        <v>38.267</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -4386,14 +4386,14 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="B153" t="n">
-        <v>33.24044531633152</v>
+        <v>37.79599999999999</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4409,14 +4409,14 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="B154" t="n">
-        <v>41.53470905162611</v>
+        <v>38.73599999999993</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4432,14 +4432,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="B155" t="n">
-        <v>16.95955468366848</v>
+        <v>39.77999999999997</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4455,14 +4455,14 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1958</v>
+        <v>1964</v>
       </c>
       <c r="B156" t="n">
-        <v>39.9</v>
+        <v>41.89499999999998</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4478,14 +4478,14 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1958</v>
+        <v>1965</v>
       </c>
       <c r="B157" t="n">
-        <v>4.110275689223058</v>
+        <v>43.19700000000006</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4501,14 +4501,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1959</v>
+        <v>1966</v>
       </c>
       <c r="B158" t="n">
-        <v>50.3</v>
+        <v>45.80600000000004</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4524,10 +4524,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1959</v>
+        <v>1967</v>
       </c>
       <c r="B159" t="n">
-        <v>38.33099999999999</v>
+        <v>46.762</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -4547,14 +4547,14 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1959</v>
+        <v>1968</v>
       </c>
       <c r="B160" t="n">
-        <v>30.72764001728608</v>
+        <v>48.75099999999998</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4570,14 +4570,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1959</v>
+        <v>1969</v>
       </c>
       <c r="B161" t="n">
-        <v>42.95298199052133</v>
+        <v>50.76300000000003</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4593,14 +4593,14 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1959</v>
+        <v>1970</v>
       </c>
       <c r="B162" t="n">
-        <v>19.57235998271392</v>
+        <v>51.98900000000009</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4616,14 +4616,14 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1959</v>
+        <v>1971</v>
       </c>
       <c r="B163" t="n">
-        <v>51.1</v>
+        <v>52.56099999999998</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4639,14 +4639,14 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1959</v>
+        <v>1972</v>
       </c>
       <c r="B164" t="n">
-        <v>3.528375733855186</v>
+        <v>55.01400000000001</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4662,14 +4662,14 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1960</v>
+        <v>1973</v>
       </c>
       <c r="B165" t="n">
-        <v>50.7</v>
+        <v>61.5150000000001</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4685,10 +4685,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1960</v>
+        <v>1974</v>
       </c>
       <c r="B166" t="n">
-        <v>38.267</v>
+        <v>66.05999999999983</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -4708,14 +4708,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1960</v>
+        <v>1975</v>
       </c>
       <c r="B167" t="n">
-        <v>32.21911092646448</v>
+        <v>69.77800000000002</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4731,14 +4731,14 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1960</v>
+        <v>1976</v>
       </c>
       <c r="B168" t="n">
-        <v>43.77963375485327</v>
+        <v>75.99900000000002</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4754,14 +4754,14 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1960</v>
+        <v>1977</v>
       </c>
       <c r="B169" t="n">
-        <v>18.48088907353552</v>
+        <v>81.66799999999989</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4777,14 +4777,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1960</v>
+        <v>1978</v>
       </c>
       <c r="B170" t="n">
-        <v>50</v>
+        <v>90.29499999999996</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4800,14 +4800,14 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1960</v>
+        <v>1979</v>
       </c>
       <c r="B171" t="n">
-        <v>3.814</v>
+        <v>100.8139999999999</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4823,14 +4823,14 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1961</v>
+        <v>1980</v>
       </c>
       <c r="B172" t="n">
-        <v>53.2</v>
+        <v>108.614</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1961</v>
+        <v>1981</v>
       </c>
       <c r="B173" t="n">
-        <v>37.79599999999999</v>
+        <v>115.895</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -4869,14 +4869,14 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1961</v>
+        <v>1982</v>
       </c>
       <c r="B174" t="n">
-        <v>34.41015659229209</v>
+        <v>121.5840000000001</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4892,14 +4892,14 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1961</v>
+        <v>1983</v>
       </c>
       <c r="B175" t="n">
-        <v>44.47656366585564</v>
+        <v>127.8460000000002</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4915,14 +4915,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1961</v>
+        <v>1984</v>
       </c>
       <c r="B176" t="n">
-        <v>18.78984340770792</v>
+        <v>140.5839999999998</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4938,14 +4938,14 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1961</v>
+        <v>1985</v>
       </c>
       <c r="B177" t="n">
-        <v>50.9</v>
+        <v>151.1699999999996</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4961,14 +4961,14 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1961</v>
+        <v>1986</v>
       </c>
       <c r="B178" t="n">
-        <v>3.842829076620825</v>
+        <v>158.797</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4984,14 +4984,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1962</v>
+        <v>1987</v>
       </c>
       <c r="B179" t="n">
-        <v>55.3</v>
+        <v>165.6610000000003</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5007,10 +5007,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1962</v>
+        <v>1988</v>
       </c>
       <c r="B180" t="n">
-        <v>38.73599999999993</v>
+        <v>185.3589999999999</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -5030,14 +5030,14 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1962</v>
+        <v>1989</v>
       </c>
       <c r="B181" t="n">
-        <v>34.86042433234423</v>
+        <v>198.6359999999995</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5053,14 +5053,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1962</v>
+        <v>1990</v>
       </c>
       <c r="B182" t="n">
-        <v>45.52982999529251</v>
+        <v>212.0709999999999</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5076,14 +5076,14 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1962</v>
+        <v>1991</v>
       </c>
       <c r="B183" t="n">
-        <v>20.43957566765577</v>
+        <v>215.5700000000006</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5099,14 +5099,14 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1962</v>
+        <v>1992</v>
       </c>
       <c r="B184" t="n">
-        <v>58.6</v>
+        <v>226.3560000000002</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5122,14 +5122,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1962</v>
+        <v>1993</v>
       </c>
       <c r="B185" t="n">
-        <v>3.600682593856656</v>
+        <v>240.107</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5145,14 +5145,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1963</v>
+        <v>1994</v>
       </c>
       <c r="B186" t="n">
-        <v>56.5</v>
+        <v>253.9400000000001</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5168,10 +5168,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1963</v>
+        <v>1995</v>
       </c>
       <c r="B187" t="n">
-        <v>39.77999999999997</v>
+        <v>268.4709999999995</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -5191,14 +5191,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1963</v>
+        <v>1996</v>
       </c>
       <c r="B188" t="n">
-        <v>34.9292543554007</v>
+        <v>284.7640000000006</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5214,14 +5214,14 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1963</v>
+        <v>1997</v>
       </c>
       <c r="B189" t="n">
-        <v>45.53013761080626</v>
+        <v>303.4410000000003</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5237,14 +5237,14 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1963</v>
+        <v>1998</v>
       </c>
       <c r="B190" t="n">
-        <v>21.5707456445993</v>
+        <v>330.2030000000009</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5260,14 +5260,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1963</v>
+        <v>1999</v>
       </c>
       <c r="B191" t="n">
-        <v>64.3</v>
+        <v>360.5170000000003</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5283,14 +5283,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1963</v>
+        <v>2000</v>
       </c>
       <c r="B192" t="n">
-        <v>3.463452566096423</v>
+        <v>390.6469999999999</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5306,14 +5306,14 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1964</v>
+        <v>2001</v>
       </c>
       <c r="B193" t="n">
-        <v>59.4</v>
+        <v>462.0970000000007</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5329,10 +5329,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1964</v>
+        <v>2002</v>
       </c>
       <c r="B194" t="n">
-        <v>41.89499999999998</v>
+        <v>493.0770000000002</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -5352,14 +5352,14 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1964</v>
+        <v>2003</v>
       </c>
       <c r="B195" t="n">
-        <v>36.1899629390912</v>
+        <v>533.1810000000005</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5375,14 +5375,14 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1964</v>
+        <v>2004</v>
       </c>
       <c r="B196" t="n">
-        <v>47.37283348506166</v>
+        <v>588.5650000000005</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5398,14 +5398,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1964</v>
+        <v>2005</v>
       </c>
       <c r="B197" t="n">
-        <v>23.2100370609088</v>
+        <v>642.3470000000007</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5421,14 +5421,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1964</v>
+        <v>2006</v>
       </c>
       <c r="B198" t="n">
-        <v>71.09999999999999</v>
+        <v>712.5430000000006</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5444,14 +5444,14 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1964</v>
+        <v>2007</v>
       </c>
       <c r="B199" t="n">
-        <v>3.364275668073136</v>
+        <v>781.262999999999</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5467,14 +5467,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1965</v>
+        <v>2008</v>
       </c>
       <c r="B200" t="n">
-        <v>63.9</v>
+        <v>797.9680000000017</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1965</v>
+        <v>2009</v>
       </c>
       <c r="B201" t="n">
-        <v>43.19700000000006</v>
+        <v>761.3919999999989</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -5513,14 +5513,14 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1965</v>
+        <v>2010</v>
       </c>
       <c r="B202" t="n">
-        <v>38.26191220368743</v>
+        <v>776.8859999999995</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5536,14 +5536,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1965</v>
+        <v>2011</v>
       </c>
       <c r="B203" t="n">
-        <v>48.23125714172195</v>
+        <v>811.2930000000006</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5559,14 +5559,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1965</v>
+        <v>1947</v>
       </c>
       <c r="B204" t="n">
-        <v>25.63808779631257</v>
+        <v>22.13317399617591</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5582,14 +5582,14 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1965</v>
+        <v>1948</v>
       </c>
       <c r="B205" t="n">
-        <v>81.8</v>
+        <v>23.49115492957747</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5605,14 +5605,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1965</v>
+        <v>1949</v>
       </c>
       <c r="B206" t="n">
-        <v>3.177261613691931</v>
+        <v>20.64184536082474</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5628,14 +5628,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1966</v>
+        <v>1950</v>
       </c>
       <c r="B207" t="n">
-        <v>68.2</v>
+        <v>21.08311044327573</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5651,14 +5651,14 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1966</v>
+        <v>1951</v>
       </c>
       <c r="B208" t="n">
-        <v>45.80600000000004</v>
+        <v>24.4311164606376</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5674,10 +5674,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1966</v>
+        <v>1952</v>
       </c>
       <c r="B209" t="n">
-        <v>41.55317928286852</v>
+        <v>25.97801874999999</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -5697,14 +5697,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1966</v>
+        <v>1953</v>
       </c>
       <c r="B210" t="n">
-        <v>49.02199016915122</v>
+        <v>25.81271453590193</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5720,14 +5720,14 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1966</v>
+        <v>1954</v>
       </c>
       <c r="B211" t="n">
-        <v>26.64682071713148</v>
+        <v>26.22484460260972</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5743,14 +5743,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1966</v>
+        <v>1955</v>
       </c>
       <c r="B212" t="n">
-        <v>88</v>
+        <v>25.34998326359831</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5766,14 +5766,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1966</v>
+        <v>1956</v>
       </c>
       <c r="B213" t="n">
-        <v>3.278409090909091</v>
+        <v>27.89066666666666</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5789,14 +5789,14 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1967</v>
+        <v>1957</v>
       </c>
       <c r="B214" t="n">
-        <v>69.8</v>
+        <v>30.07444786729856</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5812,14 +5812,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1967</v>
+        <v>1958</v>
       </c>
       <c r="B215" t="n">
-        <v>46.762</v>
+        <v>33.24044531633152</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5835,10 +5835,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1967</v>
+        <v>1959</v>
       </c>
       <c r="B216" t="n">
-        <v>44.52220721178262</v>
+        <v>30.72764001728608</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -5858,14 +5858,14 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1967</v>
+        <v>1960</v>
       </c>
       <c r="B217" t="n">
-        <v>50.43153830484621</v>
+        <v>32.21911092646448</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5881,14 +5881,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1967</v>
+        <v>1961</v>
       </c>
       <c r="B218" t="n">
-        <v>25.27779278821738</v>
+        <v>34.41015659229209</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5904,14 +5904,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="B219" t="n">
-        <v>85.40000000000001</v>
+        <v>34.86042433234423</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5927,14 +5927,14 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="B220" t="n">
-        <v>3.611241217798594</v>
+        <v>34.9292543554007</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5950,14 +5950,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1968</v>
+        <v>1964</v>
       </c>
       <c r="B221" t="n">
-        <v>74.2</v>
+        <v>36.1899629390912</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5973,14 +5973,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="B222" t="n">
-        <v>48.75099999999998</v>
+        <v>38.26191220368743</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5996,10 +5996,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B223" t="n">
-        <v>48.1840341880342</v>
+        <v>41.55317928286852</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -6019,14 +6019,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B224" t="n">
-        <v>53.47939506306501</v>
+        <v>44.52220721178262</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6045,11 +6045,11 @@
         <v>1968</v>
       </c>
       <c r="B225" t="n">
-        <v>26.01596581196581</v>
+        <v>48.1840341880342</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6065,14 +6065,14 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B226" t="n">
-        <v>91.59999999999999</v>
+        <v>53.33211639871382</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6088,14 +6088,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B227" t="n">
-        <v>3.725982532751092</v>
+        <v>57.81271951219511</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6111,14 +6111,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B228" t="n">
-        <v>77.5</v>
+        <v>61.12371918208375</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6134,14 +6134,14 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B229" t="n">
-        <v>50.76300000000003</v>
+        <v>69.20973781337047</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6157,10 +6157,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="B230" t="n">
-        <v>53.33211639871382</v>
+        <v>83.77466355866353</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -6180,14 +6180,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="B231" t="n">
-        <v>57.96568546576879</v>
+        <v>87.89350167858709</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6203,14 +6203,14 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="B232" t="n">
-        <v>24.16788360128617</v>
+        <v>88.95773091603053</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6226,14 +6226,14 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1969</v>
+        <v>1976</v>
       </c>
       <c r="B233" t="n">
-        <v>87.90000000000001</v>
+        <v>96.24894097346184</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6249,14 +6249,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="B234" t="n">
-        <v>4.30716723549488</v>
+        <v>104.9365393211488</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6272,14 +6272,14 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="B235" t="n">
-        <v>78.5</v>
+        <v>121.5507545106616</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6295,14 +6295,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="B236" t="n">
-        <v>51.98900000000009</v>
+        <v>136.768343530964</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6318,10 +6318,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1970</v>
+        <v>1980</v>
       </c>
       <c r="B237" t="n">
-        <v>57.81271951219511</v>
+        <v>137.0868719384185</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -6341,14 +6341,14 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="B238" t="n">
-        <v>60.86097266329525</v>
+        <v>141.4248939732143</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6364,14 +6364,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="B239" t="n">
-        <v>20.68728048780489</v>
+        <v>139.8255161224351</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6387,14 +6387,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1970</v>
+        <v>1983</v>
       </c>
       <c r="B240" t="n">
-        <v>75.40000000000001</v>
+        <v>145.716558326528</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6410,14 +6410,14 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1970</v>
+        <v>1984</v>
       </c>
       <c r="B241" t="n">
-        <v>5.307692307692308</v>
+        <v>174.4225190712178</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6433,14 +6433,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1971</v>
+        <v>1985</v>
       </c>
       <c r="B242" t="n">
-        <v>84.7</v>
+        <v>185.0835726210351</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6456,14 +6456,14 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1971</v>
+        <v>1986</v>
       </c>
       <c r="B243" t="n">
-        <v>52.56099999999998</v>
+        <v>204.5789705277931</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6479,10 +6479,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1971</v>
+        <v>1987</v>
       </c>
       <c r="B244" t="n">
-        <v>61.12371918208375</v>
+        <v>226.1087194184646</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -6502,14 +6502,14 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1971</v>
+        <v>1988</v>
       </c>
       <c r="B245" t="n">
-        <v>65.30661776322812</v>
+        <v>252.9911632340426</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6525,14 +6525,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1971</v>
+        <v>1989</v>
       </c>
       <c r="B246" t="n">
-        <v>23.57628081791626</v>
+        <v>270.9997701393715</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6548,14 +6548,14 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1971</v>
+        <v>1990</v>
       </c>
       <c r="B247" t="n">
-        <v>88.2</v>
+        <v>284.2644836264166</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6571,14 +6571,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1971</v>
+        <v>1991</v>
       </c>
       <c r="B248" t="n">
-        <v>4.821995464852607</v>
+        <v>282.912160291993</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6594,14 +6594,14 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="B249" t="n">
-        <v>96</v>
+        <v>317.9531645822911</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6617,14 +6617,14 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1972</v>
+        <v>1993</v>
       </c>
       <c r="B250" t="n">
-        <v>55.01400000000001</v>
+        <v>340.6473003045685</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6640,10 +6640,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1972</v>
+        <v>1994</v>
       </c>
       <c r="B251" t="n">
-        <v>69.20973781337047</v>
+        <v>357.413675551788</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -6663,14 +6663,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1972</v>
+        <v>1995</v>
       </c>
       <c r="B252" t="n">
-        <v>70.67819242304112</v>
+        <v>372.177239585785</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6686,14 +6686,14 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1972</v>
+        <v>1996</v>
       </c>
       <c r="B253" t="n">
-        <v>26.79026218662953</v>
+        <v>415.624920318725</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6709,14 +6709,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1972</v>
+        <v>1997</v>
       </c>
       <c r="B254" t="n">
-        <v>101.9</v>
+        <v>442.5738979544756</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6732,14 +6732,14 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1972</v>
+        <v>1998</v>
       </c>
       <c r="B255" t="n">
-        <v>4.636898920510304</v>
+        <v>511.616931912821</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6755,14 +6755,14 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1973</v>
+        <v>1999</v>
       </c>
       <c r="B256" t="n">
-        <v>113.6</v>
+        <v>560.3269442178117</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6778,14 +6778,14 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1973</v>
+        <v>2000</v>
       </c>
       <c r="B257" t="n">
-        <v>61.5150000000001</v>
+        <v>641.5149170252795</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6801,10 +6801,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1973</v>
+        <v>2001</v>
       </c>
       <c r="B258" t="n">
-        <v>83.77466355866353</v>
+        <v>692.6827946834177</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -6824,14 +6824,14 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1973</v>
+        <v>2002</v>
       </c>
       <c r="B259" t="n">
-        <v>76.42871110965802</v>
+        <v>679.8322276677316</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6847,14 +6847,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1973</v>
+        <v>2003</v>
       </c>
       <c r="B260" t="n">
-        <v>29.82533644133646</v>
+        <v>688.8938135231316</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6870,14 +6870,14 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1973</v>
+        <v>2004</v>
       </c>
       <c r="B261" t="n">
-        <v>109.6</v>
+        <v>715.3362120841025</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6893,14 +6893,14 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1973</v>
+        <v>2005</v>
       </c>
       <c r="B262" t="n">
-        <v>4.871350364963504</v>
+        <v>705.3272803275531</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6916,14 +6916,14 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1974</v>
+        <v>2006</v>
       </c>
       <c r="B263" t="n">
-        <v>113.5</v>
+        <v>723.7641857126449</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6939,14 +6939,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1974</v>
+        <v>2007</v>
       </c>
       <c r="B264" t="n">
-        <v>66.05999999999983</v>
+        <v>734.7659385966354</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6962,10 +6962,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1974</v>
+        <v>2008</v>
       </c>
       <c r="B265" t="n">
-        <v>87.89350167858709</v>
+        <v>825.9123928626207</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -6985,14 +6985,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1974</v>
+        <v>2009</v>
       </c>
       <c r="B266" t="n">
-        <v>85.12484052898959</v>
+        <v>677.1568942464602</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7008,14 +7008,14 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1974</v>
+        <v>2010</v>
       </c>
       <c r="B267" t="n">
-        <v>25.60649832141291</v>
+        <v>702.9835422014145</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7031,14 +7031,14 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1974</v>
+        <v>2011</v>
       </c>
       <c r="B268" t="n">
-        <v>97.7</v>
+        <v>733.3709996586977</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7054,14 +7054,14 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1974</v>
+        <v>1947</v>
       </c>
       <c r="B269" t="n">
-        <v>6.012282497441146</v>
+        <v>27.89235982558716</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7077,14 +7077,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1975</v>
+        <v>1948</v>
       </c>
       <c r="B270" t="n">
-        <v>119.6</v>
+        <v>30.06280873588836</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7100,14 +7100,14 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1975</v>
+        <v>1949</v>
       </c>
       <c r="B271" t="n">
-        <v>69.77800000000002</v>
+        <v>30.30337862900169</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7123,14 +7123,14 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1975</v>
+        <v>1950</v>
       </c>
       <c r="B272" t="n">
-        <v>88.95773091603053</v>
+        <v>31.9388483418088</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7146,10 +7146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1975</v>
+        <v>1951</v>
       </c>
       <c r="B273" t="n">
-        <v>92.34144511737324</v>
+        <v>33.74244602423543</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -7169,14 +7169,14 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1975</v>
+        <v>1952</v>
       </c>
       <c r="B274" t="n">
-        <v>30.64226908396947</v>
+        <v>35.55068966543091</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7192,14 +7192,14 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1975</v>
+        <v>1953</v>
       </c>
       <c r="B275" t="n">
-        <v>118.7</v>
+        <v>36.97894610202118</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7215,14 +7215,14 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1975</v>
+        <v>1954</v>
       </c>
       <c r="B276" t="n">
-        <v>5.180286436394271</v>
+        <v>37.41459002647837</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7238,14 +7238,14 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1976</v>
+        <v>1955</v>
       </c>
       <c r="B277" t="n">
-        <v>132.2</v>
+        <v>38.59418068542845</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7261,14 +7261,14 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1976</v>
+        <v>1956</v>
       </c>
       <c r="B278" t="n">
-        <v>75.99900000000002</v>
+        <v>40.05854873369148</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7284,14 +7284,14 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1976</v>
+        <v>1957</v>
       </c>
       <c r="B279" t="n">
-        <v>96.24894097346184</v>
+        <v>41.13117066038148</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7307,10 +7307,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1976</v>
+        <v>1958</v>
       </c>
       <c r="B280" t="n">
-        <v>99.89854666773856</v>
+        <v>41.53470905162611</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -7330,14 +7330,14 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1976</v>
+        <v>1959</v>
       </c>
       <c r="B281" t="n">
-        <v>35.95105902653815</v>
+        <v>42.95298199052133</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7353,14 +7353,14 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1976</v>
+        <v>1960</v>
       </c>
       <c r="B282" t="n">
-        <v>145.1</v>
+        <v>43.77963375485326</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7376,14 +7376,14 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1976</v>
+        <v>1961</v>
       </c>
       <c r="B283" t="n">
-        <v>4.791178497587871</v>
+        <v>44.47656366585564</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7399,14 +7399,14 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1977</v>
+        <v>1962</v>
       </c>
       <c r="B284" t="n">
-        <v>146</v>
+        <v>45.52982999529251</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7422,14 +7422,14 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1977</v>
+        <v>1963</v>
       </c>
       <c r="B285" t="n">
-        <v>81.66799999999989</v>
+        <v>45.53013761080626</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7445,14 +7445,14 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1977</v>
+        <v>1964</v>
       </c>
       <c r="B286" t="n">
-        <v>104.9365393211488</v>
+        <v>47.37283348506166</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7468,10 +7468,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1977</v>
+        <v>1965</v>
       </c>
       <c r="B287" t="n">
-        <v>111.3519143121816</v>
+        <v>48.23125714172195</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -7491,14 +7491,14 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1977</v>
+        <v>1966</v>
       </c>
       <c r="B288" t="n">
-        <v>41.06346067885116</v>
+        <v>49.02199016915122</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7514,14 +7514,14 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="B289" t="n">
-        <v>172.7</v>
+        <v>50.43153830484621</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7537,14 +7537,14 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1977</v>
+        <v>1968</v>
       </c>
       <c r="B290" t="n">
-        <v>4.544296467863347</v>
+        <v>53.47939506306501</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7560,14 +7560,14 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1978</v>
+        <v>1969</v>
       </c>
       <c r="B291" t="n">
-        <v>167.5</v>
+        <v>57.96568546576879</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7583,14 +7583,14 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1978</v>
+        <v>1970</v>
       </c>
       <c r="B292" t="n">
-        <v>90.29499999999996</v>
+        <v>60.86097266329525</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7606,14 +7606,14 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1978</v>
+        <v>1971</v>
       </c>
       <c r="B293" t="n">
-        <v>121.5507545106616</v>
+        <v>65.30661776322812</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7629,10 +7629,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1978</v>
+        <v>1972</v>
       </c>
       <c r="B294" t="n">
-        <v>125.8669655776218</v>
+        <v>70.67819242304112</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -7652,14 +7652,14 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="B295" t="n">
-        <v>45.94924548933842</v>
+        <v>76.42871110965802</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -7675,14 +7675,14 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="B296" t="n">
-        <v>195.6</v>
+        <v>85.12484052898959</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7698,14 +7698,14 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="B297" t="n">
-        <v>4.610429447852761</v>
+        <v>92.34144511737324</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7721,14 +7721,14 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="B298" t="n">
-        <v>181.1</v>
+        <v>99.89854666773856</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7744,14 +7744,14 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B299" t="n">
-        <v>100.8139999999998</v>
+        <v>111.3519143121816</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7767,14 +7767,14 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B300" t="n">
-        <v>136.768343530964</v>
+        <v>125.8669655776218</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7813,14 +7813,14 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B302" t="n">
-        <v>44.33165646903601</v>
+        <v>160.6194559598636</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7836,14 +7836,14 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B303" t="n">
-        <v>190.7</v>
+        <v>177.0563089272547</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7859,14 +7859,14 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="B304" t="n">
-        <v>5.359202936549554</v>
+        <v>195.1049007659867</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7882,14 +7882,14 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B305" t="n">
-        <v>173.5</v>
+        <v>211.3799946280874</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7905,14 +7905,14 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1980</v>
+        <v>1984</v>
       </c>
       <c r="B306" t="n">
-        <v>108.614</v>
+        <v>225.821743242517</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7928,14 +7928,14 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="B307" t="n">
-        <v>137.0868719384185</v>
+        <v>233.6549190302999</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7951,10 +7951,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1980</v>
+        <v>1986</v>
       </c>
       <c r="B308" t="n">
-        <v>160.6194559598636</v>
+        <v>244.9544067020715</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -7974,14 +7974,14 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1980</v>
+        <v>1987</v>
       </c>
       <c r="B309" t="n">
-        <v>36.41312806158152</v>
+        <v>262.7665165791017</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7997,14 +7997,14 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="B310" t="n">
-        <v>166</v>
+        <v>284.4048981579043</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8020,14 +8020,14 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1980</v>
+        <v>1989</v>
       </c>
       <c r="B311" t="n">
-        <v>6.747590361445782</v>
+        <v>296.6903722005354</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8043,14 +8043,14 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="B312" t="n">
-        <v>181.6</v>
+        <v>313.1064019532254</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8066,14 +8066,14 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1981</v>
+        <v>1991</v>
       </c>
       <c r="B313" t="n">
-        <v>115.895</v>
+        <v>335.1858685628636</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8089,14 +8089,14 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1981</v>
+        <v>1992</v>
       </c>
       <c r="B314" t="n">
-        <v>141.4248939732143</v>
+        <v>342.6369558715313</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8112,10 +8112,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="B315" t="n">
-        <v>177.0563089272547</v>
+        <v>368.0253699918709</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -8135,14 +8135,14 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1981</v>
+        <v>1994</v>
       </c>
       <c r="B316" t="n">
-        <v>40.17510602678573</v>
+        <v>379.2731368856792</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8158,14 +8158,14 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1981</v>
+        <v>1995</v>
       </c>
       <c r="B317" t="n">
-        <v>193.6</v>
+        <v>385.736521102357</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8181,14 +8181,14 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="B318" t="n">
-        <v>6.404958677685951</v>
+        <v>396.5606261625491</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8204,14 +8204,14 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="B319" t="n">
-        <v>174.8</v>
+        <v>412.947226668047</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8227,14 +8227,14 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1982</v>
+        <v>1998</v>
       </c>
       <c r="B320" t="n">
-        <v>121.5840000000001</v>
+        <v>427.2383869271452</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8250,14 +8250,14 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1982</v>
+        <v>1999</v>
       </c>
       <c r="B321" t="n">
-        <v>139.8255161224351</v>
+        <v>436.3638988079471</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -8273,10 +8273,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1982</v>
+        <v>2000</v>
       </c>
       <c r="B322" t="n">
-        <v>195.1049007659868</v>
+        <v>468.3893431431777</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -8296,14 +8296,14 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1982</v>
+        <v>2001</v>
       </c>
       <c r="B323" t="n">
-        <v>34.97448387756495</v>
+        <v>476.5141632649148</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8319,14 +8319,14 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1982</v>
+        <v>2002</v>
       </c>
       <c r="B324" t="n">
-        <v>173.1</v>
+        <v>481.6627815496646</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8342,14 +8342,14 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1982</v>
+        <v>2003</v>
       </c>
       <c r="B325" t="n">
-        <v>7.474292316580011</v>
+        <v>520.3967329241192</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8365,14 +8365,14 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>1983</v>
+        <v>2004</v>
       </c>
       <c r="B326" t="n">
-        <v>190.7</v>
+        <v>545.9301591203856</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8388,14 +8388,14 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>1983</v>
+        <v>2005</v>
       </c>
       <c r="B327" t="n">
-        <v>127.8460000000002</v>
+        <v>565.9187782082371</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8411,14 +8411,14 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>1983</v>
+        <v>2006</v>
       </c>
       <c r="B328" t="n">
-        <v>145.716558326528</v>
+        <v>595.7026751530897</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8434,10 +8434,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1983</v>
+        <v>2007</v>
       </c>
       <c r="B329" t="n">
-        <v>211.3799946280874</v>
+        <v>608.6083835626497</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -8457,14 +8457,14 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>1983</v>
+        <v>2008</v>
       </c>
       <c r="B330" t="n">
-        <v>44.98344167347199</v>
+        <v>605.4491089634998</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8480,14 +8480,14 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>1983</v>
+        <v>2009</v>
       </c>
       <c r="B331" t="n">
-        <v>224.8</v>
+        <v>598.7911075719613</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -8503,14 +8503,14 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>1983</v>
+        <v>2010</v>
       </c>
       <c r="B332" t="n">
-        <v>6.081405693950177</v>
+        <v>606.653512306897</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8526,14 +8526,14 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>1984</v>
+        <v>2011</v>
       </c>
       <c r="B333" t="n">
-        <v>233.1</v>
+        <v>610.030511314913</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-D</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8549,14 +8549,14 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1984</v>
+        <v>1947</v>
       </c>
       <c r="B334" t="n">
-        <v>140.5839999999998</v>
+        <v>12.36682600382409</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8572,14 +8572,14 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1984</v>
+        <v>1948</v>
       </c>
       <c r="B335" t="n">
-        <v>174.4225190712178</v>
+        <v>15.70884507042253</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -8595,14 +8595,14 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1984</v>
+        <v>1949</v>
       </c>
       <c r="B336" t="n">
-        <v>225.821743242517</v>
+        <v>13.95815463917527</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -8618,10 +8618,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1984</v>
+        <v>1950</v>
       </c>
       <c r="B337" t="n">
-        <v>58.67748092878219</v>
+        <v>16.41688955672427</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -8641,14 +8641,14 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1984</v>
+        <v>1951</v>
       </c>
       <c r="B338" t="n">
-        <v>282</v>
+        <v>18.2688835393624</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -8664,14 +8664,14 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1984</v>
+        <v>1952</v>
       </c>
       <c r="B339" t="n">
-        <v>5.368439716312057</v>
+        <v>17.12198125000001</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8687,14 +8687,14 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1985</v>
+        <v>1953</v>
       </c>
       <c r="B340" t="n">
-        <v>246.1</v>
+        <v>16.18728546409807</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8710,14 +8710,14 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1985</v>
+        <v>1954</v>
       </c>
       <c r="B341" t="n">
-        <v>151.1699999999996</v>
+        <v>16.07515539739027</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -8733,14 +8733,14 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1985</v>
+        <v>1955</v>
       </c>
       <c r="B342" t="n">
-        <v>185.0835726210352</v>
+        <v>18.95001673640169</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8756,14 +8756,14 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1985</v>
+        <v>1956</v>
       </c>
       <c r="B343" t="n">
-        <v>233.6549190302999</v>
+        <v>18.00933333333334</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1985</v>
+        <v>1957</v>
       </c>
       <c r="B344" t="n">
-        <v>61.01642737896486</v>
+        <v>17.72555213270143</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -8802,14 +8802,14 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="B345" t="n">
-        <v>294.4</v>
+        <v>16.95955468366848</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8825,14 +8825,14 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1985</v>
+        <v>1959</v>
       </c>
       <c r="B346" t="n">
-        <v>5.510869565217392</v>
+        <v>19.57235998271391</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8848,14 +8848,14 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1986</v>
+        <v>1960</v>
       </c>
       <c r="B347" t="n">
-        <v>262.6</v>
+        <v>18.48088907353552</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8871,14 +8871,14 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1986</v>
+        <v>1961</v>
       </c>
       <c r="B348" t="n">
-        <v>158.7970000000001</v>
+        <v>18.78984340770791</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8894,14 +8894,14 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1986</v>
+        <v>1962</v>
       </c>
       <c r="B349" t="n">
-        <v>204.5789705277931</v>
+        <v>20.43957566765577</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8917,14 +8917,14 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1986</v>
+        <v>1963</v>
       </c>
       <c r="B350" t="n">
-        <v>244.9544067020716</v>
+        <v>21.5707456445993</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8940,10 +8940,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1986</v>
+        <v>1964</v>
       </c>
       <c r="B351" t="n">
-        <v>58.02102947220692</v>
+        <v>23.2100370609088</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -8963,14 +8963,14 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1986</v>
+        <v>1965</v>
       </c>
       <c r="B352" t="n">
-        <v>274.7</v>
+        <v>25.63808779631257</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8986,14 +8986,14 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="B353" t="n">
-        <v>6.262832180560612</v>
+        <v>26.64682071713148</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9009,14 +9009,14 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1987</v>
+        <v>1967</v>
       </c>
       <c r="B354" t="n">
-        <v>294.2</v>
+        <v>25.27779278821738</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9032,14 +9032,14 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1987</v>
+        <v>1968</v>
       </c>
       <c r="B355" t="n">
-        <v>165.6610000000003</v>
+        <v>26.01596581196581</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9055,14 +9055,14 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1987</v>
+        <v>1969</v>
       </c>
       <c r="B356" t="n">
-        <v>226.1087194184646</v>
+        <v>24.16788360128618</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -9078,14 +9078,14 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1987</v>
+        <v>1970</v>
       </c>
       <c r="B357" t="n">
-        <v>262.7665165791017</v>
+        <v>20.68728048780489</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9101,10 +9101,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1987</v>
+        <v>1971</v>
       </c>
       <c r="B358" t="n">
-        <v>68.09128058153539</v>
+        <v>23.57628081791626</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -9124,14 +9124,14 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1987</v>
+        <v>1972</v>
       </c>
       <c r="B359" t="n">
-        <v>319.8</v>
+        <v>26.79026218662953</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9147,14 +9147,14 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1987</v>
+        <v>1973</v>
       </c>
       <c r="B360" t="n">
-        <v>5.753595997498437</v>
+        <v>29.82533644133646</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9170,14 +9170,14 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1988</v>
+        <v>1974</v>
       </c>
       <c r="B361" t="n">
-        <v>334.8</v>
+        <v>25.60649832141291</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9193,14 +9193,14 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1988</v>
+        <v>1975</v>
       </c>
       <c r="B362" t="n">
-        <v>185.3589999999999</v>
+        <v>30.64226908396947</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9216,14 +9216,14 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1988</v>
+        <v>1976</v>
       </c>
       <c r="B363" t="n">
-        <v>252.9911632340426</v>
+        <v>35.95105902653815</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9239,14 +9239,14 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1988</v>
+        <v>1977</v>
       </c>
       <c r="B364" t="n">
-        <v>284.4048981579043</v>
+        <v>41.06346067885116</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9262,10 +9262,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1988</v>
+        <v>1978</v>
       </c>
       <c r="B365" t="n">
-        <v>81.80883676595744</v>
+        <v>45.94924548933842</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -9285,14 +9285,14 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1988</v>
+        <v>1979</v>
       </c>
       <c r="B366" t="n">
-        <v>369.6</v>
+        <v>44.33165646903601</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9308,14 +9308,14 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1988</v>
+        <v>1980</v>
       </c>
       <c r="B367" t="n">
-        <v>5.358225108225108</v>
+        <v>36.41312806158152</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9331,14 +9331,14 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1989</v>
+        <v>1981</v>
       </c>
       <c r="B368" t="n">
-        <v>351.6</v>
+        <v>40.17510602678573</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9354,14 +9354,14 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1989</v>
+        <v>1982</v>
       </c>
       <c r="B369" t="n">
-        <v>198.6359999999995</v>
+        <v>34.97448387756495</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9377,14 +9377,14 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1989</v>
+        <v>1983</v>
       </c>
       <c r="B370" t="n">
-        <v>270.9997701393715</v>
+        <v>44.98344167347199</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9400,14 +9400,14 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="B371" t="n">
-        <v>296.6903722005354</v>
+        <v>58.67748092878219</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9423,10 +9423,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1989</v>
+        <v>1985</v>
       </c>
       <c r="B372" t="n">
-        <v>80.60022986062853</v>
+        <v>61.01642737896486</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -9446,14 +9446,14 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="B373" t="n">
-        <v>358.4</v>
+        <v>58.02102947220692</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9469,14 +9469,14 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B374" t="n">
-        <v>5.826729910714287</v>
+        <v>68.09128058153539</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9492,14 +9492,14 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B375" t="n">
-        <v>365.1</v>
+        <v>81.80883676595744</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9515,14 +9515,14 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B376" t="n">
-        <v>212.0709999999999</v>
+        <v>80.60022986062853</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9541,11 +9541,11 @@
         <v>1990</v>
       </c>
       <c r="B377" t="n">
-        <v>284.2644836264166</v>
+        <v>80.83551637358346</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9561,14 +9561,14 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B378" t="n">
-        <v>313.1064019532254</v>
+        <v>84.38783970800705</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B379" t="n">
-        <v>80.83551637358346</v>
+        <v>96.94683541770888</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -9607,14 +9607,14 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="B380" t="n">
-        <v>358.4</v>
+        <v>108.9526996954315</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9630,14 +9630,14 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1990</v>
+        <v>1994</v>
       </c>
       <c r="B381" t="n">
-        <v>6.140066964285714</v>
+        <v>127.686324448212</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9653,14 +9653,14 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="B382" t="n">
-        <v>367.3</v>
+        <v>143.822760414215</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9676,14 +9676,14 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="B383" t="n">
-        <v>215.5700000000006</v>
+        <v>168.075079681275</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9699,14 +9699,14 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="B384" t="n">
-        <v>282.912160291993</v>
+        <v>185.6261020455245</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -9722,14 +9722,14 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="B385" t="n">
-        <v>335.1858685628636</v>
+        <v>175.883068087179</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9745,10 +9745,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1991</v>
+        <v>1999</v>
       </c>
       <c r="B386" t="n">
-        <v>84.38783970800705</v>
+        <v>186.4730557821882</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -9768,14 +9768,14 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="B387" t="n">
-        <v>380.8</v>
+        <v>175.9850829747205</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -9791,14 +9791,14 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="B388" t="n">
-        <v>5.90703781512605</v>
+        <v>178.0172053165824</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -9814,14 +9814,14 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1992</v>
+        <v>2002</v>
       </c>
       <c r="B389" t="n">
-        <v>414.9</v>
+        <v>210.4677723322684</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -9837,14 +9837,14 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="B390" t="n">
-        <v>226.3560000000003</v>
+        <v>241.7061864768684</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -9860,14 +9860,14 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1992</v>
+        <v>2004</v>
       </c>
       <c r="B391" t="n">
-        <v>317.9531645822911</v>
+        <v>318.4637879158975</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9883,14 +9883,14 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1992</v>
+        <v>2005</v>
       </c>
       <c r="B392" t="n">
-        <v>342.6369558715313</v>
+        <v>364.4727196724468</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9906,10 +9906,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="B393" t="n">
-        <v>96.94683541770888</v>
+        <v>409.2358142873551</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -9929,14 +9929,14 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1992</v>
+        <v>2007</v>
       </c>
       <c r="B394" t="n">
-        <v>423.1</v>
+        <v>355.6340614033647</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9952,14 +9952,14 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1992</v>
+        <v>2008</v>
       </c>
       <c r="B395" t="n">
-        <v>5.614511935712597</v>
+        <v>271.9876071373794</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9975,14 +9975,14 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1993</v>
+        <v>2009</v>
       </c>
       <c r="B396" t="n">
-        <v>449.6</v>
+        <v>302.2431057535398</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -9998,14 +9998,14 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="B397" t="n">
-        <v>240.107</v>
+        <v>400.4164577985856</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10021,14 +10021,14 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1993</v>
+        <v>2011</v>
       </c>
       <c r="B398" t="n">
-        <v>340.6473003045685</v>
+        <v>423.9290003413023</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-E</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -10044,14 +10044,14 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1993</v>
+        <v>1947</v>
       </c>
       <c r="B399" t="n">
-        <v>368.0253699918709</v>
+        <v>22.5</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -10067,14 +10067,14 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1993</v>
+        <v>1948</v>
       </c>
       <c r="B400" t="n">
-        <v>108.9526996954315</v>
+        <v>29.6</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -10090,10 +10090,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1993</v>
+        <v>1949</v>
       </c>
       <c r="B401" t="n">
-        <v>466.8</v>
+        <v>27.6</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -10113,14 +10113,14 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1993</v>
+        <v>1950</v>
       </c>
       <c r="B402" t="n">
-        <v>5.330334190231362</v>
+        <v>34.4</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -10136,14 +10136,14 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1994</v>
+        <v>1951</v>
       </c>
       <c r="B403" t="n">
-        <v>485.1</v>
+        <v>39.1</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -10159,14 +10159,14 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1994</v>
+        <v>1952</v>
       </c>
       <c r="B404" t="n">
-        <v>253.94</v>
+        <v>37</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10182,14 +10182,14 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1994</v>
+        <v>1953</v>
       </c>
       <c r="B405" t="n">
-        <v>357.413675551788</v>
+        <v>37.3</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -10205,14 +10205,14 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1994</v>
+        <v>1954</v>
       </c>
       <c r="B406" t="n">
-        <v>379.2731368856792</v>
+        <v>36.4</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -10228,14 +10228,14 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1994</v>
+        <v>1955</v>
       </c>
       <c r="B407" t="n">
-        <v>127.686324448212</v>
+        <v>46.6</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10251,10 +10251,10 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>1994</v>
+        <v>1956</v>
       </c>
       <c r="B408" t="n">
-        <v>550.3</v>
+        <v>45.2</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -10274,14 +10274,14 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>1994</v>
+        <v>1957</v>
       </c>
       <c r="B409" t="n">
-        <v>4.787933854261313</v>
+        <v>44.5</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -10297,14 +10297,14 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1995</v>
+        <v>1958</v>
       </c>
       <c r="B410" t="n">
-        <v>516</v>
+        <v>39.9</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -10320,14 +10320,14 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1995</v>
+        <v>1959</v>
       </c>
       <c r="B411" t="n">
-        <v>268.4709999999995</v>
+        <v>51.1</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10343,14 +10343,14 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1995</v>
+        <v>1960</v>
       </c>
       <c r="B412" t="n">
-        <v>372.177239585785</v>
+        <v>50</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10366,14 +10366,14 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>1995</v>
+        <v>1961</v>
       </c>
       <c r="B413" t="n">
-        <v>385.736521102357</v>
+        <v>50.9</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10389,14 +10389,14 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1995</v>
+        <v>1962</v>
       </c>
       <c r="B414" t="n">
-        <v>143.822760414215</v>
+        <v>58.6</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10412,10 +10412,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="B415" t="n">
-        <v>623.2</v>
+        <v>64.3</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -10435,14 +10435,14 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>1995</v>
+        <v>1964</v>
       </c>
       <c r="B416" t="n">
-        <v>4.454428754813864</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10458,14 +10458,14 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1996</v>
+        <v>1965</v>
       </c>
       <c r="B417" t="n">
-        <v>583.7</v>
+        <v>81.8</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -10481,14 +10481,14 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>1996</v>
+        <v>1966</v>
       </c>
       <c r="B418" t="n">
-        <v>284.7640000000006</v>
+        <v>88</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -10504,14 +10504,14 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1996</v>
+        <v>1967</v>
       </c>
       <c r="B419" t="n">
-        <v>415.624920318725</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -10527,14 +10527,14 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1996</v>
+        <v>1968</v>
       </c>
       <c r="B420" t="n">
-        <v>396.5606261625491</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -10550,14 +10550,14 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>1996</v>
+        <v>1969</v>
       </c>
       <c r="B421" t="n">
-        <v>168.075079681275</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -10573,10 +10573,10 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1996</v>
+        <v>1970</v>
       </c>
       <c r="B422" t="n">
-        <v>699.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -10596,14 +10596,14 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1996</v>
+        <v>1971</v>
       </c>
       <c r="B423" t="n">
-        <v>4.167119370979271</v>
+        <v>88.2</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10619,14 +10619,14 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1997</v>
+        <v>1972</v>
       </c>
       <c r="B424" t="n">
-        <v>628.2</v>
+        <v>101.9</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10642,14 +10642,14 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1997</v>
+        <v>1973</v>
       </c>
       <c r="B425" t="n">
-        <v>303.4410000000003</v>
+        <v>109.6</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10665,14 +10665,14 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1997</v>
+        <v>1974</v>
       </c>
       <c r="B426" t="n">
-        <v>442.5738979544756</v>
+        <v>97.7</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10688,14 +10688,14 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>1997</v>
+        <v>1975</v>
       </c>
       <c r="B427" t="n">
-        <v>412.947226668047</v>
+        <v>118.7</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -10711,14 +10711,14 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1997</v>
+        <v>1976</v>
       </c>
       <c r="B428" t="n">
-        <v>185.6261020455245</v>
+        <v>145.1</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -10734,10 +10734,10 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>1997</v>
+        <v>1977</v>
       </c>
       <c r="B429" t="n">
-        <v>777.3</v>
+        <v>172.7</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -10757,14 +10757,14 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1997</v>
+        <v>1978</v>
       </c>
       <c r="B430" t="n">
-        <v>4.018911617136241</v>
+        <v>195.6</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -10780,14 +10780,14 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>1998</v>
+        <v>1979</v>
       </c>
       <c r="B431" t="n">
-        <v>687.5</v>
+        <v>190.7</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -10803,14 +10803,14 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>1998</v>
+        <v>1980</v>
       </c>
       <c r="B432" t="n">
-        <v>330.2030000000009</v>
+        <v>166</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -10826,14 +10826,14 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1998</v>
+        <v>1981</v>
       </c>
       <c r="B433" t="n">
-        <v>511.616931912821</v>
+        <v>193.6</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -10849,14 +10849,14 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1998</v>
+        <v>1982</v>
       </c>
       <c r="B434" t="n">
-        <v>427.2383869271452</v>
+        <v>173.1</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -10872,14 +10872,14 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1998</v>
+        <v>1983</v>
       </c>
       <c r="B435" t="n">
-        <v>175.883068087179</v>
+        <v>224.8</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1998</v>
+        <v>1984</v>
       </c>
       <c r="B436" t="n">
-        <v>709.7</v>
+        <v>282</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -10918,14 +10918,14 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1998</v>
+        <v>1985</v>
       </c>
       <c r="B437" t="n">
-        <v>4.786247710300127</v>
+        <v>294.4</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -10941,14 +10941,14 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1999</v>
+        <v>1986</v>
       </c>
       <c r="B438" t="n">
-        <v>746.8</v>
+        <v>274.7</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -10964,14 +10964,14 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>1999</v>
+        <v>1987</v>
       </c>
       <c r="B439" t="n">
-        <v>360.5170000000003</v>
+        <v>319.8</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -10987,14 +10987,14 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1999</v>
+        <v>1988</v>
       </c>
       <c r="B440" t="n">
-        <v>560.3269442178117</v>
+        <v>369.6</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -11010,14 +11010,14 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="B441" t="n">
-        <v>436.3638988079471</v>
+        <v>358.4</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -11033,14 +11033,14 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1999</v>
+        <v>1990</v>
       </c>
       <c r="B442" t="n">
-        <v>186.4730557821883</v>
+        <v>358.4</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -11056,10 +11056,10 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B443" t="n">
-        <v>734.8</v>
+        <v>380.8</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -11079,14 +11079,14 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="B444" t="n">
-        <v>4.938214480130648</v>
+        <v>423.1</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -11102,14 +11102,14 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="B445" t="n">
-        <v>817.5</v>
+        <v>466.8</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -11125,14 +11125,14 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="B446" t="n">
-        <v>390.6469999999999</v>
+        <v>550.3</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -11148,14 +11148,14 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="B447" t="n">
-        <v>641.5149170252795</v>
+        <v>623.2</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -11171,14 +11171,14 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="B448" t="n">
-        <v>468.3893431431777</v>
+        <v>699.5</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -11194,14 +11194,14 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="B449" t="n">
-        <v>175.9850829747205</v>
+        <v>777.3</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -11217,10 +11217,10 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B450" t="n">
-        <v>673.6</v>
+        <v>709.7</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -11240,14 +11240,14 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B451" t="n">
-        <v>5.865053444180522</v>
+        <v>734.8</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -11263,14 +11263,14 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B452" t="n">
-        <v>870.7</v>
+        <v>673.6</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -11289,11 +11289,11 @@
         <v>2001</v>
       </c>
       <c r="B453" t="n">
-        <v>462.0970000000007</v>
+        <v>614.5</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -11309,14 +11309,14 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B454" t="n">
-        <v>692.6827946834177</v>
+        <v>714.3</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -11332,14 +11332,14 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B455" t="n">
-        <v>476.5141632649148</v>
+        <v>812</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -11355,14 +11355,14 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="B456" t="n">
-        <v>178.0172053165824</v>
+        <v>1041.9</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -11378,10 +11378,10 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="B457" t="n">
-        <v>614.5</v>
+        <v>1216.6</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -11401,14 +11401,14 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="B458" t="n">
-        <v>6.486899918633035</v>
+        <v>1351.5</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>XS002-G</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -11424,14 +11424,14 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="B459" t="n">
-        <v>890.3</v>
+        <v>1159.8</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -11447,14 +11447,14 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B460" t="n">
-        <v>493.0770000000002</v>
+        <v>841.8</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -11470,14 +11470,14 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>2002</v>
+        <v>2009</v>
       </c>
       <c r="B461" t="n">
-        <v>679.8322276677316</v>
+        <v>989.5</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -11493,14 +11493,14 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="B462" t="n">
-        <v>481.6627815496646</v>
+        <v>1300.9</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11516,14 +11516,14 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="B463" t="n">
-        <v>210.4677723322684</v>
+        <v>1388.1</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-F</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -11539,14 +11539,14 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>2002</v>
+        <v>1947</v>
       </c>
       <c r="B464" t="n">
-        <v>714.3</v>
+        <v>3.648888888888889</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -11556,16 +11556,16 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>2002</v>
+        <v>1948</v>
       </c>
       <c r="B465" t="n">
-        <v>5.572868542629148</v>
+        <v>3.077702702702702</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -11579,20 +11579,20 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>2003</v>
+        <v>1949</v>
       </c>
       <c r="B466" t="n">
-        <v>930.6</v>
+        <v>3.217391304347826</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -11602,20 +11602,20 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>2003</v>
+        <v>1950</v>
       </c>
       <c r="B467" t="n">
-        <v>533.1810000000005</v>
+        <v>2.869186046511628</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -11625,20 +11625,20 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>2003</v>
+        <v>1951</v>
       </c>
       <c r="B468" t="n">
-        <v>688.8938135231316</v>
+        <v>2.930946291560102</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -11648,20 +11648,20 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>2003</v>
+        <v>1952</v>
       </c>
       <c r="B469" t="n">
-        <v>520.3967329241192</v>
+        <v>3.324324324324324</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -11671,20 +11671,20 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>2003</v>
+        <v>1953</v>
       </c>
       <c r="B470" t="n">
-        <v>241.7061864768684</v>
+        <v>3.592493297587132</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -11694,20 +11694,20 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>2003</v>
+        <v>1954</v>
       </c>
       <c r="B471" t="n">
-        <v>812</v>
+        <v>3.631868131868132</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -11717,16 +11717,16 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>2003</v>
+        <v>1955</v>
       </c>
       <c r="B472" t="n">
-        <v>5.056034482758621</v>
+        <v>3.103004291845493</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -11740,20 +11740,20 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>2004</v>
+        <v>1956</v>
       </c>
       <c r="B473" t="n">
-        <v>1033.8</v>
+        <v>3.5</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -11763,20 +11763,20 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>2004</v>
+        <v>1957</v>
       </c>
       <c r="B474" t="n">
-        <v>588.5650000000005</v>
+        <v>3.741573033707865</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -11786,20 +11786,20 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>2004</v>
+        <v>1958</v>
       </c>
       <c r="B475" t="n">
-        <v>715.3362120841025</v>
+        <v>4.110275689223058</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -11809,20 +11809,20 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>2004</v>
+        <v>1959</v>
       </c>
       <c r="B476" t="n">
-        <v>545.9301591203856</v>
+        <v>3.528375733855186</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -11832,20 +11832,20 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>2004</v>
+        <v>1960</v>
       </c>
       <c r="B477" t="n">
-        <v>318.4637879158975</v>
+        <v>3.814</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -11855,20 +11855,20 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>2004</v>
+        <v>1961</v>
       </c>
       <c r="B478" t="n">
-        <v>1041.9</v>
+        <v>3.842829076620825</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -11878,16 +11878,16 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>2004</v>
+        <v>1962</v>
       </c>
       <c r="B479" t="n">
-        <v>4.094346866301947</v>
+        <v>3.600682593856655</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -11901,20 +11901,20 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>2005</v>
+        <v>1963</v>
       </c>
       <c r="B480" t="n">
-        <v>1069.8</v>
+        <v>3.463452566096423</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -11924,20 +11924,20 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>2005</v>
+        <v>1964</v>
       </c>
       <c r="B481" t="n">
-        <v>642.3470000000007</v>
+        <v>3.364275668073136</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -11947,20 +11947,20 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>2005</v>
+        <v>1965</v>
       </c>
       <c r="B482" t="n">
-        <v>705.3272803275531</v>
+        <v>3.177261613691931</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -11970,20 +11970,20 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>2005</v>
+        <v>1966</v>
       </c>
       <c r="B483" t="n">
-        <v>565.9187782082371</v>
+        <v>3.278409090909091</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -11993,20 +11993,20 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>2005</v>
+        <v>1967</v>
       </c>
       <c r="B484" t="n">
-        <v>364.4727196724468</v>
+        <v>3.611241217798594</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -12016,20 +12016,20 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>2005</v>
+        <v>1968</v>
       </c>
       <c r="B485" t="n">
-        <v>1216.6</v>
+        <v>3.725982532751092</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -12039,16 +12039,16 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>2005</v>
+        <v>1969</v>
       </c>
       <c r="B486" t="n">
-        <v>3.697599868485945</v>
+        <v>4.30716723549488</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -12062,20 +12062,20 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>2006</v>
+        <v>1970</v>
       </c>
       <c r="B487" t="n">
-        <v>1133</v>
+        <v>5.307692307692307</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -12085,20 +12085,20 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>2006</v>
+        <v>1971</v>
       </c>
       <c r="B488" t="n">
-        <v>712.5430000000006</v>
+        <v>4.821995464852607</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -12108,20 +12108,20 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>2006</v>
+        <v>1972</v>
       </c>
       <c r="B489" t="n">
-        <v>723.7641857126449</v>
+        <v>4.636898920510304</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -12131,20 +12131,20 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>2006</v>
+        <v>1973</v>
       </c>
       <c r="B490" t="n">
-        <v>595.7026751530897</v>
+        <v>4.871350364963503</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -12154,20 +12154,20 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>2006</v>
+        <v>1974</v>
       </c>
       <c r="B491" t="n">
-        <v>409.2358142873551</v>
+        <v>6.012282497441146</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -12177,20 +12177,20 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>2006</v>
+        <v>1975</v>
       </c>
       <c r="B492" t="n">
-        <v>1351.5</v>
+        <v>5.180286436394271</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -12200,16 +12200,16 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>2006</v>
+        <v>1976</v>
       </c>
       <c r="B493" t="n">
-        <v>3.509729929707732</v>
+        <v>4.791178497587871</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -12223,20 +12223,20 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2007</v>
+        <v>1977</v>
       </c>
       <c r="B494" t="n">
-        <v>1090.4</v>
+        <v>4.544296467863347</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -12246,20 +12246,20 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>2007</v>
+        <v>1978</v>
       </c>
       <c r="B495" t="n">
-        <v>781.262999999999</v>
+        <v>4.610429447852761</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -12269,20 +12269,20 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>2007</v>
+        <v>1979</v>
       </c>
       <c r="B496" t="n">
-        <v>734.7659385966354</v>
+        <v>5.359202936549554</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -12292,20 +12292,20 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2007</v>
+        <v>1980</v>
       </c>
       <c r="B497" t="n">
-        <v>608.6083835626497</v>
+        <v>6.747590361445782</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -12315,20 +12315,20 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>2007</v>
+        <v>1981</v>
       </c>
       <c r="B498" t="n">
-        <v>355.6340614033647</v>
+        <v>6.404958677685951</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -12338,20 +12338,20 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>2007</v>
+        <v>1982</v>
       </c>
       <c r="B499" t="n">
-        <v>1159.8</v>
+        <v>7.474292316580011</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -12361,16 +12361,16 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>2007</v>
+        <v>1983</v>
       </c>
       <c r="B500" t="n">
-        <v>4.262890153474737</v>
+        <v>6.081405693950177</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -12384,20 +12384,20 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>2008</v>
+        <v>1984</v>
       </c>
       <c r="B501" t="n">
-        <v>1097.9</v>
+        <v>5.368439716312057</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -12407,20 +12407,20 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>2008</v>
+        <v>1985</v>
       </c>
       <c r="B502" t="n">
-        <v>797.9680000000017</v>
+        <v>5.510869565217392</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -12430,20 +12430,20 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>2008</v>
+        <v>1986</v>
       </c>
       <c r="B503" t="n">
-        <v>825.9123928626207</v>
+        <v>6.262832180560612</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -12453,20 +12453,20 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>2008</v>
+        <v>1987</v>
       </c>
       <c r="B504" t="n">
-        <v>605.4491089634998</v>
+        <v>5.753595997498437</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -12476,20 +12476,20 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="B505" t="n">
-        <v>271.9876071373794</v>
+        <v>5.358225108225108</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -12499,20 +12499,20 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>2008</v>
+        <v>1989</v>
       </c>
       <c r="B506" t="n">
-        <v>841.8</v>
+        <v>5.826729910714286</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -12522,16 +12522,16 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="B507" t="n">
-        <v>5.970420527441197</v>
+        <v>6.140066964285714</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -12545,20 +12545,20 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>2009</v>
+        <v>1991</v>
       </c>
       <c r="B508" t="n">
-        <v>979.4</v>
+        <v>5.90703781512605</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -12568,20 +12568,20 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>2009</v>
+        <v>1992</v>
       </c>
       <c r="B509" t="n">
-        <v>761.3919999999989</v>
+        <v>5.614511935712597</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -12591,20 +12591,20 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="B510" t="n">
-        <v>677.1568942464602</v>
+        <v>5.330334190231362</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -12614,20 +12614,20 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="B511" t="n">
-        <v>598.7911075719613</v>
+        <v>4.787933854261313</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -12637,20 +12637,20 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>2009</v>
+        <v>1995</v>
       </c>
       <c r="B512" t="n">
-        <v>302.2431057535398</v>
+        <v>4.454428754813864</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -12660,20 +12660,20 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="B513" t="n">
-        <v>989.5</v>
+        <v>4.167119370979271</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -12683,16 +12683,16 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="B514" t="n">
-        <v>4.759575543203638</v>
+        <v>4.018911617136241</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -12706,20 +12706,20 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>2010</v>
+        <v>1998</v>
       </c>
       <c r="B515" t="n">
-        <v>1103.4</v>
+        <v>4.786247710300127</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -12729,20 +12729,20 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="B516" t="n">
-        <v>776.8859999999995</v>
+        <v>4.938214480130648</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -12752,20 +12752,20 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="B517" t="n">
-        <v>702.9835422014145</v>
+        <v>5.865053444180522</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -12775,20 +12775,20 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="B518" t="n">
-        <v>606.653512306897</v>
+        <v>6.486899918633035</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -12798,20 +12798,20 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B519" t="n">
-        <v>400.4164577985856</v>
+        <v>5.572868542629148</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -12821,20 +12821,20 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="B520" t="n">
-        <v>1300.9</v>
+        <v>5.056034482758621</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -12844,16 +12844,16 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="B521" t="n">
-        <v>3.695825966638481</v>
+        <v>4.094346866301947</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -12867,20 +12867,20 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="B522" t="n">
-        <v>1157.3</v>
+        <v>3.697599868485945</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>XS002-A</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -12890,20 +12890,20 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B523" t="n">
-        <v>811.2930000000006</v>
+        <v>3.509729929707732</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>XS002-B</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -12913,20 +12913,20 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B524" t="n">
-        <v>733.3709996586977</v>
+        <v>4.262890153474737</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>XS002-C</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -12936,20 +12936,20 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B525" t="n">
-        <v>610.030511314913</v>
+        <v>5.970420527441197</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>XS002-D</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -12959,20 +12959,20 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B526" t="n">
-        <v>423.9290003413023</v>
+        <v>4.759575543203638</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>XS002-E</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -12982,20 +12982,20 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B527" t="n">
-        <v>1388.1</v>
+        <v>3.695825966638481</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>XS002-F</t>
+          <t>XS002-G</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WEQ2 = (sigma*PropInc - ECprop)/(1+sigma). Source: Appendix Table 6.8.I.2. Used by XS003 / S603. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>WEQ2 = (sigma*PropInc - ECprop)/(1+sigma). Source: Appendix Table 6.8.I.2. Used by XS003 and S603.</t>
         </is>
       </c>
     </row>
@@ -13206,7 +13206,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau (Historical Statistics 1975, for IRS book values), and the Federal Reserve Board G.17 industrial-production release (FRB G.17). All public domain.</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13326,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>`V03_XS002_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The validation step round-trips the constructed series against the Appendix 6.8 source workbook at a 1.0% tolerance. Two data-sourcing steps needed for this construction are resolved: the remap of financial services indirectly measured (FISIM) in NIPA Table 7.11, and the 1993 BEA depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13369,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS002 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Under the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline, and following the principle that extended values must be rebuilt from sources rather than spliced, **extension does NOT splice the published XS002 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -13379,14 +13379,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>1. Fetch the BEA NIPA tables via the BEA data API (a BEA API key is required), using the table ids documented for this series' primary source.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>2. Fetch BEA Fixed Asset Tables 6.1, 6.4, 6.7, 6.8 from the same source.</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13416,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>For XS002, the Phase 5 round-trip validation reads `XS002_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS002, the round-trip validation reads the raw series from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Source substitutions</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Forecast vs. observed data</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the staged 1993 BEA depreciation inputs).</t>
         </is>
       </c>
     </row>
@@ -13490,35 +13490,35 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | The load step returns a FAIL status naming the missing file |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | The load step records 0 rows for that subseries; validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The documented re-fetch script logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| FISIM (financial services indirectly measured) revision to NIPA Table 7.11 line numbers (affects XS003) | The Table 7.11 line resolver falls back to the nearest pinned vintage with a logged warning | Lines are re-mapped by their published stub labels; the vintage used is logged |</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | The capital-stock series (XS004 and related) freeze depreciation-rate inputs at the 2011-vintage projection | Documented with the staged 1993 BEA methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Comparison with the earlier replication</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>Round-trip parity with an earlier replication is expected within tolerance for the book period. The comparison against that earlier replication's per-series output is informational only, when available.</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension integrity</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension MUST re-fetch the BEA, IRS, and Federal Reserve Board (FRB) component series and re-compute the formula end-to-end; splicing the published series is forbidden. The loader caches BEA and FRED responses for 30 days (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:47:15.068411+00:00</t>
+          <t>2026-07-02T06:26:33.139407+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS002_extenbook.xlsx
+++ b/extenbooks/XS002_extenbook.xlsx
@@ -14105,7 +14105,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:33.139407+00:00</t>
+          <t>2026-07-11T03:44:27.115071+00:00</t>
         </is>
       </c>
     </row>
@@ -14120,11 +14120,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14147,6 +14147,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Six dollar components of the WEQ2 wage-equivalent adjustment and the corporate/non-corporate profit split, plus the dimensionless Sigma ratio. Feeds XS003/S603. Appendix Table 6.8.I.2. Latent mixed-units: XS002-G (Sigma = corporate EC/profit) is a dimensionless ratio (2.87-7.47), not dollars, so units are now declared per-subseries to keep the chart honest (Sigma must not share a billions axis with the dollar components).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS002_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS002_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WEQ2 = (sigma*PropInc - ECprop)/(1+sigma). Source: Appendix Table 6.8.I.2. Used by XS003 / S603.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
